--- a/DAY6/TestCase01.xlsx
+++ b/DAY6/TestCase01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42e3a53505992cf3/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{BC1B2DF0-A016-446A-9BFD-5022C9B2DE75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA063609-DD86-419C-B4F9-05B370E5B6F9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F94F980-BEEE-4F79-A7E4-BF051A5715CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{14E08236-D79B-4C45-99E5-296E99175371}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{14E08236-D79B-4C45-99E5-296E99175371}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,9 +57,6 @@
     <t>chrome</t>
   </si>
   <si>
-    <t>https://opensource-demo.orangehrmlive.com/web/index.php/pim/addEmployee</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
@@ -103,6 +100,9 @@
   </si>
   <si>
     <t>A . Kavya</t>
+  </si>
+  <si>
+    <t>https://opensource-demo.orangehrmlive.com/web/index.php/auth/login?lang=en</t>
   </si>
 </sst>
 </file>
@@ -510,25 +510,25 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" t="s">
-        <v>12</v>
-      </c>
       <c r="I1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>17</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>18</v>
-      </c>
-      <c r="M1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -536,40 +536,40 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
       </c>
       <c r="F2">
         <v>4550</v>
       </c>
       <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" t="s">
         <v>20</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/DAY6/TestCase01.xlsx
+++ b/DAY6/TestCase01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42e3a53505992cf3/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F94F980-BEEE-4F79-A7E4-BF051A5715CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{8EA6827D-819F-4F3F-9947-FE590DEDD1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{14E08236-D79B-4C45-99E5-296E99175371}"/>
   </bookViews>
